--- a/data/trans_bre/P6906-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 10,22</t>
+          <t>-21,64; 12,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 12,63</t>
+          <t>-25,28; 12,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 15,27</t>
+          <t>-28,13; 16,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 24,89</t>
+          <t>-8,04; 25,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 41,27</t>
+          <t>-55,78; 54,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,53; 48,66</t>
+          <t>-54,12; 44,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 43,43</t>
+          <t>-49,67; 51,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 145,62</t>
+          <t>-22,28; 162,52</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 20,91</t>
+          <t>-14,67; 19,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 20,61</t>
+          <t>-24,8; 18,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 19,58</t>
+          <t>-29,31; 19,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 28,48</t>
+          <t>-6,63; 30,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 206,04</t>
+          <t>-53,42; 188,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,43; 137,28</t>
+          <t>-72,6; 117,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 115,81</t>
+          <t>-66,0; 113,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 281,31</t>
+          <t>-28,49; 287,02</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 15,82</t>
+          <t>-31,6; 13,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 27,36</t>
+          <t>-11,37; 25,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 54,94</t>
+          <t>-14,05; 56,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 33,09</t>
+          <t>-9,75; 29,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,06</t>
+          <t>-100,0; 76,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 161,22</t>
+          <t>-47,6; 153,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 369,74</t>
+          <t>-54,63; 396,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 339,29</t>
+          <t>-50,52; 270,57</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 20,44</t>
+          <t>-6,46; 20,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 22,22</t>
+          <t>-5,88; 23,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 23,7</t>
+          <t>-2,03; 23,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 13,78</t>
+          <t>-7,39; 14,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 117,81</t>
+          <t>-27,57; 124,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 123,47</t>
+          <t>-23,42; 142,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 127,97</t>
+          <t>-8,75; 124,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 87,89</t>
+          <t>-25,66; 87,48</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 16,67</t>
+          <t>-7,83; 16,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 27,85</t>
+          <t>-15,97; 27,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 31,68</t>
+          <t>1,99; 30,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 20,82</t>
+          <t>-3,5; 21,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 278,51</t>
+          <t>-47,76; 266,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,71; 180,2</t>
+          <t>-43,88; 182,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 832,29</t>
+          <t>-4,54; 644,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 1337,88</t>
+          <t>-28,27; 1337,13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,58</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,74</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -1160,160 +1160,59 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,47; 6,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,43; 12,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,83; 16,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,95; 13,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-29,74; 33,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,58; 53,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,24; 80,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,67; 88,34</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,58</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8,74</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,18%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>32,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-7,6; 5,66</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 12,51</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,7; 17,14</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-3,34; 12,63</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-29,87; 28,61</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-14,34; 54,22</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,76; 81,76</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-13,75; 78,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>

--- a/data/trans_bre/P6906-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 12,71</t>
+          <t>-21,78; 13,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 12,39</t>
+          <t>-24,38; 13,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 16,84</t>
+          <t>-28,95; 14,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 25,97</t>
+          <t>-10,97; 24,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 54,84</t>
+          <t>-55,46; 60,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 44,71</t>
+          <t>-53,63; 49,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-49,67; 51,72</t>
+          <t>-51,01; 41,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 162,52</t>
+          <t>-28,12; 136,54</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,92</t>
+          <t>12,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 19,78</t>
+          <t>-16,35; 21,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 18,71</t>
+          <t>-26,98; 16,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 19,12</t>
+          <t>-29,68; 18,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 30,88</t>
+          <t>-7,31; 28,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 188,21</t>
+          <t>-59,74; 208,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 117,6</t>
+          <t>-74,59; 112,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 113,59</t>
+          <t>-67,82; 108,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 287,02</t>
+          <t>-27,68; 268,5</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,67</t>
+          <t>9,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 13,09</t>
+          <t>-32,98; 13,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 25,63</t>
+          <t>-11,79; 26,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 56,02</t>
+          <t>-11,88; 55,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 29,52</t>
+          <t>-11,34; 29,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 76,89</t>
+          <t>-100,0; 70,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,6; 153,69</t>
+          <t>-45,42; 165,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 396,46</t>
+          <t>-50,88; 399,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,52; 270,57</t>
+          <t>-49,4; 225,92</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 20,71</t>
+          <t>-5,66; 20,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 23,58</t>
+          <t>-6,08; 21,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 23,08</t>
+          <t>-2,39; 24,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 14,17</t>
+          <t>-10,91; 11,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 124,55</t>
+          <t>-28,32; 122,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 142,07</t>
+          <t>-22,73; 120,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 124,29</t>
+          <t>-9,63; 135,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 87,48</t>
+          <t>-35,73; 67,06</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,07</t>
+          <t>18,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>187,24%</t>
+          <t>399,59%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 16,51</t>
+          <t>-8,32; 18,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 27,18</t>
+          <t>-15,8; 27,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 30,86</t>
+          <t>2,26; 30,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 21,45</t>
+          <t>8,83; 26,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 266,98</t>
+          <t>-49,74; 286,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,88; 182,27</t>
+          <t>-44,33; 171,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 644,15</t>
+          <t>0,62; 762,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 1337,13</t>
+          <t>72,27; 2652,69</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 6,84</t>
+          <t>-7,67; 5,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 12,31</t>
+          <t>-4,49; 11,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 16,8</t>
+          <t>0,82; 16,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 13,21</t>
+          <t>1,01; 13,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 33,56</t>
+          <t>-31,36; 29,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 53,88</t>
+          <t>-16,32; 45,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 80,58</t>
+          <t>2,56; 82,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 88,34</t>
+          <t>4,26; 84,2</t>
         </is>
       </c>
     </row>
